--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117971076</v>
+        <v>117971054</v>
       </c>
       <c r="B4" t="n">
-        <v>56549</v>
+        <v>56695</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +958,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117971054</v>
+        <v>117971076</v>
       </c>
       <c r="B5" t="n">
-        <v>56695</v>
+        <v>56549</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102952</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,14 +1082,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117971058</v>
+        <v>117971054</v>
       </c>
       <c r="B3" t="n">
-        <v>57691</v>
+        <v>56696</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,33 +815,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>102952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117971054</v>
+        <v>117971058</v>
       </c>
       <c r="B4" t="n">
-        <v>56695</v>
+        <v>57692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,33 +939,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102952</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
         <v>117971076</v>
       </c>
       <c r="B5" t="n">
-        <v>56549</v>
+        <v>56550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,6 +1169,386 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118136509</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56934</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fiskmås</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Larus canus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509246</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6574372</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118136553</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>509246</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6574372</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118136493</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56633</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>509246</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6574372</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118298160</v>
+        <v>118297850</v>
       </c>
       <c r="B9" t="n">
-        <v>56936</v>
+        <v>57385</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,20 +1559,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102964</v>
+        <v>102626</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1585,11 +1585,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1795,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118297850</v>
+        <v>118298374</v>
       </c>
       <c r="B11" t="n">
-        <v>57385</v>
+        <v>56922</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,41 +1811,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102626</v>
+        <v>102963</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118298339</v>
+        <v>118297834</v>
       </c>
       <c r="B12" t="n">
-        <v>56698</v>
+        <v>56744</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,20 +1935,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102952</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1965,7 +1965,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118297834</v>
+        <v>118298121</v>
       </c>
       <c r="B13" t="n">
-        <v>56744</v>
+        <v>56552</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2059,20 +2059,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>102976</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2082,14 +2082,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118298121</v>
+        <v>118298339</v>
       </c>
       <c r="B14" t="n">
-        <v>56552</v>
+        <v>56698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2183,20 +2183,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102976</v>
+        <v>102952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118297837</v>
+        <v>118298160</v>
       </c>
       <c r="B15" t="n">
-        <v>56635</v>
+        <v>56936</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2307,25 +2307,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>102964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118298374</v>
+        <v>118297837</v>
       </c>
       <c r="B16" t="n">
-        <v>56922</v>
+        <v>56635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,20 +2431,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102963</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2454,14 +2454,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118676207</v>
+        <v>118676245</v>
       </c>
       <c r="B17" t="n">
-        <v>57148</v>
+        <v>56552</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2555,20 +2555,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100100</v>
+        <v>102976</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2582,11 +2582,7 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -2645,11 +2641,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ivrigt lockande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2676,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118676245</v>
+        <v>118676207</v>
       </c>
       <c r="B18" t="n">
-        <v>56552</v>
+        <v>57148</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2688,20 +2679,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102976</v>
+        <v>100100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2715,7 +2706,11 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -2774,6 +2769,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ivrigt lockande.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -1675,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118298064</v>
+        <v>118298374</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>56922</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,33 +1691,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>102963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118298374</v>
+        <v>118298064</v>
       </c>
       <c r="B11" t="n">
-        <v>56922</v>
+        <v>57993</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1815,33 +1815,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102963</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118297850</v>
+        <v>118298339</v>
       </c>
       <c r="B9" t="n">
-        <v>57385</v>
+        <v>56698</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,41 +1559,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102626</v>
+        <v>102952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1675,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118298374</v>
+        <v>118298121</v>
       </c>
       <c r="B10" t="n">
-        <v>56922</v>
+        <v>56552</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,20 +1683,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102963</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1710,14 +1706,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1799,10 +1795,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118298064</v>
+        <v>118297850</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>57385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1811,20 +1807,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>102626</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1834,14 +1830,18 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118298121</v>
+        <v>118298064</v>
       </c>
       <c r="B13" t="n">
-        <v>56552</v>
+        <v>57993</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2059,37 +2059,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118298339</v>
+        <v>118298160</v>
       </c>
       <c r="B14" t="n">
-        <v>56698</v>
+        <v>56936</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2183,37 +2183,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102952</v>
+        <v>102964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118298160</v>
+        <v>118297837</v>
       </c>
       <c r="B15" t="n">
-        <v>56936</v>
+        <v>56635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2307,25 +2307,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102964</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118297837</v>
+        <v>118298374</v>
       </c>
       <c r="B16" t="n">
-        <v>56635</v>
+        <v>56922</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,20 +2431,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100065</v>
+        <v>102963</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2454,14 +2454,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118676245</v>
+        <v>118676207</v>
       </c>
       <c r="B17" t="n">
-        <v>56552</v>
+        <v>57148</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2555,20 +2555,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102976</v>
+        <v>100100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2582,7 +2582,11 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -2641,6 +2645,11 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ivrigt lockande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,10 +2676,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118676207</v>
+        <v>118676245</v>
       </c>
       <c r="B18" t="n">
-        <v>57148</v>
+        <v>56552</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2679,20 +2688,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100100</v>
+        <v>102976</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2706,11 +2715,7 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -2769,11 +2774,6 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ivrigt lockande.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118298339</v>
+        <v>118297837</v>
       </c>
       <c r="B9" t="n">
-        <v>56698</v>
+        <v>56635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,20 +1559,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102952</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1582,14 +1582,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118298121</v>
+        <v>118298374</v>
       </c>
       <c r="B10" t="n">
-        <v>56552</v>
+        <v>56922</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,20 +1683,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>102963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1706,14 +1706,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118297850</v>
+        <v>118298064</v>
       </c>
       <c r="B11" t="n">
-        <v>57385</v>
+        <v>57993</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,20 +1807,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102626</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1830,18 +1830,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1923,10 +1919,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118297834</v>
+        <v>118298121</v>
       </c>
       <c r="B12" t="n">
-        <v>56744</v>
+        <v>56552</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,20 +1931,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>102976</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1958,14 +1954,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2047,10 +2043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118298064</v>
+        <v>118298160</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>56936</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2063,16 +2059,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>102964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2082,14 +2078,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2171,10 +2167,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118298160</v>
+        <v>118297834</v>
       </c>
       <c r="B14" t="n">
-        <v>56936</v>
+        <v>56744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2183,37 +2179,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102964</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2295,10 +2291,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118297837</v>
+        <v>118297850</v>
       </c>
       <c r="B15" t="n">
-        <v>56635</v>
+        <v>57385</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2311,21 +2307,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>102626</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2333,11 +2329,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118298374</v>
+        <v>118298339</v>
       </c>
       <c r="B16" t="n">
-        <v>56922</v>
+        <v>56698</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2431,20 +2431,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102963</v>
+        <v>102952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2454,14 +2454,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2798,6 +2798,259 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120551600</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56373</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>509246</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6574372</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hörd</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120551512</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57996</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>509246</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6574372</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3053,10 +3053,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120822008</v>
+        <v>120822031</v>
       </c>
       <c r="B21" t="n">
-        <v>56401</v>
+        <v>58028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3069,16 +3069,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100045</v>
+        <v>103044</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120822031</v>
+        <v>120821975</v>
       </c>
       <c r="B22" t="n">
-        <v>58025</v>
+        <v>57370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3193,33 +3193,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120821985</v>
+        <v>120822008</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>56404</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3317,16 +3317,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120821975</v>
+        <v>120821985</v>
       </c>
       <c r="B24" t="n">
-        <v>57367</v>
+        <v>57720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3441,26 +3441,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
         <v>120822024</v>
       </c>
       <c r="B25" t="n">
-        <v>57782</v>
+        <v>57785</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489203</v>
+        <v>124489150</v>
       </c>
       <c r="B26" t="n">
-        <v>56821</v>
+        <v>56965</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100038</v>
+        <v>102954</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489150</v>
+        <v>124489203</v>
       </c>
       <c r="B27" t="n">
-        <v>56965</v>
+        <v>56821</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102954</v>
+        <v>100038</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489203</v>
+        <v>124489223</v>
       </c>
       <c r="B27" t="n">
-        <v>56821</v>
+        <v>58218</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489223</v>
+        <v>124489203</v>
       </c>
       <c r="B29" t="n">
-        <v>58218</v>
+        <v>56821</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4057,20 +4057,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B26" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,20 +3685,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489223</v>
+        <v>124489203</v>
       </c>
       <c r="B27" t="n">
-        <v>58218</v>
+        <v>56821</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489239</v>
+        <v>124489150</v>
       </c>
       <c r="B28" t="n">
-        <v>57143</v>
+        <v>56965</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,20 +3933,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489203</v>
+        <v>124489223</v>
       </c>
       <c r="B29" t="n">
-        <v>56821</v>
+        <v>58218</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4057,20 +4057,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489239</v>
+        <v>124489203</v>
       </c>
       <c r="B26" t="n">
-        <v>57143</v>
+        <v>56821</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489203</v>
+        <v>124489150</v>
       </c>
       <c r="B27" t="n">
-        <v>56821</v>
+        <v>56965</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100038</v>
+        <v>102954</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B28" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,20 +3933,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489203</v>
+        <v>124489239</v>
       </c>
       <c r="B26" t="n">
-        <v>56821</v>
+        <v>57143</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100038</v>
+        <v>102963</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489239</v>
+        <v>124489203</v>
       </c>
       <c r="B28" t="n">
-        <v>57143</v>
+        <v>56821</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489239</v>
+        <v>124489203</v>
       </c>
       <c r="B26" t="n">
-        <v>57143</v>
+        <v>56821</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B27" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489203</v>
+        <v>124489223</v>
       </c>
       <c r="B28" t="n">
-        <v>56821</v>
+        <v>58218</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,20 +3933,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489223</v>
+        <v>124489150</v>
       </c>
       <c r="B29" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4057,25 +4057,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489203</v>
+        <v>124489223</v>
       </c>
       <c r="B26" t="n">
-        <v>56821</v>
+        <v>58218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,20 +3685,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489223</v>
+        <v>124489150</v>
       </c>
       <c r="B28" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489150</v>
+        <v>124489203</v>
       </c>
       <c r="B29" t="n">
-        <v>56965</v>
+        <v>56821</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102954</v>
+        <v>100038</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489239</v>
+        <v>124489150</v>
       </c>
       <c r="B27" t="n">
-        <v>57143</v>
+        <v>56965</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B28" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,20 +3933,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489223</v>
+        <v>124489239</v>
       </c>
       <c r="B26" t="n">
-        <v>58218</v>
+        <v>57143</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103055</v>
+        <v>102963</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489239</v>
+        <v>124489223</v>
       </c>
       <c r="B28" t="n">
-        <v>57143</v>
+        <v>58218</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102963</v>
+        <v>103055</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489239</v>
+        <v>124489203</v>
       </c>
       <c r="B26" t="n">
-        <v>57143</v>
+        <v>56821</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489223</v>
+        <v>124489239</v>
       </c>
       <c r="B28" t="n">
-        <v>58218</v>
+        <v>57143</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103055</v>
+        <v>102963</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489203</v>
+        <v>124489223</v>
       </c>
       <c r="B29" t="n">
-        <v>56821</v>
+        <v>58218</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4057,20 +4057,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489203</v>
+        <v>124489223</v>
       </c>
       <c r="B26" t="n">
-        <v>56821</v>
+        <v>58218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,20 +3685,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B27" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489239</v>
+        <v>124489150</v>
       </c>
       <c r="B28" t="n">
-        <v>57143</v>
+        <v>56965</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,20 +3933,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489223</v>
+        <v>124489203</v>
       </c>
       <c r="B29" t="n">
-        <v>58218</v>
+        <v>56821</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4057,20 +4057,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489223</v>
+        <v>124489239</v>
       </c>
       <c r="B26" t="n">
-        <v>58218</v>
+        <v>57143</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103055</v>
+        <v>102963</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489239</v>
+        <v>124489203</v>
       </c>
       <c r="B27" t="n">
-        <v>57143</v>
+        <v>56821</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,25 +3809,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489150</v>
+        <v>124489223</v>
       </c>
       <c r="B28" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489203</v>
+        <v>124489150</v>
       </c>
       <c r="B29" t="n">
-        <v>56821</v>
+        <v>56965</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100038</v>
+        <v>102954</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124489239</v>
+        <v>124489203</v>
       </c>
       <c r="B26" t="n">
-        <v>57143</v>
+        <v>56821</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102963</v>
+        <v>100038</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489203</v>
+        <v>124489150</v>
       </c>
       <c r="B27" t="n">
-        <v>56821</v>
+        <v>56965</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100038</v>
+        <v>102954</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B29" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4057,20 +4057,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489150</v>
+        <v>124489239</v>
       </c>
       <c r="B27" t="n">
-        <v>56965</v>
+        <v>57143</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102954</v>
+        <v>102963</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489223</v>
+        <v>124489150</v>
       </c>
       <c r="B28" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489239</v>
+        <v>124489223</v>
       </c>
       <c r="B29" t="n">
-        <v>57143</v>
+        <v>58218</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102963</v>
+        <v>103055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -3797,10 +3797,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124489239</v>
+        <v>124489150</v>
       </c>
       <c r="B27" t="n">
-        <v>57143</v>
+        <v>56965</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3809,20 +3809,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3839,7 +3839,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124489150</v>
+        <v>124489223</v>
       </c>
       <c r="B28" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3933,25 +3933,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124489223</v>
+        <v>124489239</v>
       </c>
       <c r="B29" t="n">
-        <v>58218</v>
+        <v>57143</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103055</v>
+        <v>102963</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4167,254 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125603728</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57246</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102964</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fiskmås</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Larus canus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>509260</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6574415</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125603665</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58345</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyhem, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>509260</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6574415</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bengt Jalsborn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -4169,10 +4169,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125603728</v>
+        <v>125603665</v>
       </c>
       <c r="B30" t="n">
-        <v>57246</v>
+        <v>58345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4185,16 +4185,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102964</v>
+        <v>103055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4211,7 +4211,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125603665</v>
+        <v>125603728</v>
       </c>
       <c r="B31" t="n">
-        <v>58345</v>
+        <v>57246</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4309,16 +4309,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103055</v>
+        <v>102964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -4172,12 +4172,7 @@
         <v>125603665</v>
       </c>
       <c r="B30" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4296,12 +4291,7 @@
         <v>125603728</v>
       </c>
       <c r="B31" t="n">
-        <v>57246</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57257</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -4172,7 +4172,7 @@
         <v>125603665</v>
       </c>
       <c r="B30" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 28097-2020 artfynd.xlsx
+++ b/artfynd/A 28097-2020 artfynd.xlsx
@@ -4172,7 +4172,7 @@
         <v>125603665</v>
       </c>
       <c r="B30" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>125603728</v>
       </c>
       <c r="B31" t="n">
-        <v>57257</v>
+        <v>57258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
